--- a/licing/docs/modelo-datos/Diccionario de datos.xlsx
+++ b/licing/docs/modelo-datos/Diccionario de datos.xlsx
@@ -243,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -322,12 +322,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
@@ -699,7 +693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:K366"/>
+  <dimension ref="B2:K344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -8247,7 +8241,7 @@
       <c r="B313" s="21" t="inlineStr"/>
       <c r="C313" s="16" t="inlineStr">
         <is>
-          <t>modelo_semantico</t>
+          <t>cobertura</t>
         </is>
       </c>
       <c r="D313" s="16" t="inlineStr">
@@ -8258,12 +8252,12 @@
       <c r="E313" s="17" t="n"/>
       <c r="F313" s="18" t="inlineStr">
         <is>
-          <t>Modelo semántico usado, si aplica</t>
+          <t>Cobertura de la información evaluada</t>
         </is>
       </c>
       <c r="G313" s="18" t="inlineStr">
         <is>
-          <t>Obligatorio si hay puntuaciones</t>
+          <t>Obligatorio. completa, parcial, sin_bases</t>
         </is>
       </c>
       <c r="H313" s="19" t="n"/>
@@ -8275,23 +8269,23 @@
       <c r="B314" s="21" t="inlineStr"/>
       <c r="C314" s="16" t="inlineStr">
         <is>
-          <t>puntuacion_semantica</t>
+          <t>clasificacion</t>
         </is>
       </c>
       <c r="D314" s="16" t="inlineStr">
         <is>
-          <t>double precision</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E314" s="17" t="n"/>
       <c r="F314" s="18" t="inlineStr">
         <is>
-          <t>Similitud semántica con la oferta del hotel</t>
+          <t>Propuesta automática del filtro</t>
         </is>
       </c>
       <c r="G314" s="18" t="inlineStr">
         <is>
-          <t>Entre -1 y 1. No es porcentaje de cumplimiento</t>
+          <t>Obligatorio. preseleccionada, revision_manual, descartada</t>
         </is>
       </c>
       <c r="H314" s="19" t="n"/>
@@ -8303,23 +8297,23 @@
       <c r="B315" s="21" t="inlineStr"/>
       <c r="C315" s="16" t="inlineStr">
         <is>
-          <t>puntuacion_exclusion</t>
+          <t>motivo</t>
         </is>
       </c>
       <c r="D315" s="16" t="inlineStr">
         <is>
-          <t>double precision</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E315" s="17" t="n"/>
       <c r="F315" s="18" t="inlineStr">
         <is>
-          <t>Similitud con los criterios de exclusión</t>
+          <t>Motivo de la clasificación</t>
         </is>
       </c>
       <c r="G315" s="18" t="inlineStr">
         <is>
-          <t>Entre -1 y 1</t>
+          <t>Obligatorio</t>
         </is>
       </c>
       <c r="H315" s="19" t="n"/>
@@ -8327,27 +8321,27 @@
       <c r="J315" s="19" t="n"/>
       <c r="K315" s="20" t="n"/>
     </row>
-    <row r="316" ht="15.75" customHeight="1">
+    <row r="316" ht="30" customHeight="1">
       <c r="B316" s="21" t="inlineStr"/>
       <c r="C316" s="16" t="inlineStr">
         <is>
-          <t>cobertura</t>
+          <t>entrada_evaluada</t>
         </is>
       </c>
       <c r="D316" s="16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>jsonb</t>
         </is>
       </c>
       <c r="E316" s="17" t="n"/>
       <c r="F316" s="18" t="inlineStr">
         <is>
-          <t>Cobertura de la información evaluada</t>
+          <t>Snapshot de los datos, ítems y referencias de documentos usados</t>
         </is>
       </c>
       <c r="G316" s="18" t="inlineStr">
         <is>
-          <t>Obligatorio. completa, parcial, sin_bases</t>
+          <t>Obligatorio. Permite explicar resultados históricos</t>
         </is>
       </c>
       <c r="H316" s="19" t="n"/>
@@ -8359,23 +8353,23 @@
       <c r="B317" s="21" t="inlineStr"/>
       <c r="C317" s="16" t="inlineStr">
         <is>
-          <t>clasificacion</t>
+          <t>metadatos</t>
         </is>
       </c>
       <c r="D317" s="16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>jsonb</t>
         </is>
       </c>
       <c r="E317" s="17" t="n"/>
       <c r="F317" s="18" t="inlineStr">
         <is>
-          <t>Propuesta automática del filtro</t>
+          <t>Información complementaria de la evaluación</t>
         </is>
       </c>
       <c r="G317" s="18" t="inlineStr">
         <is>
-          <t>Obligatorio. preseleccionada, revision_manual, descartada</t>
+          <t>Obligatorio. Por defecto '{}'</t>
         </is>
       </c>
       <c r="H317" s="19" t="n"/>
@@ -8384,210 +8378,214 @@
       <c r="K317" s="20" t="n"/>
     </row>
     <row r="318" ht="15.75" customHeight="1">
-      <c r="B318" s="21" t="inlineStr"/>
-      <c r="C318" s="16" t="inlineStr">
-        <is>
-          <t>motivo</t>
-        </is>
-      </c>
-      <c r="D318" s="16" t="inlineStr">
+      <c r="B318" s="22" t="inlineStr"/>
+      <c r="C318" s="23" t="inlineStr">
+        <is>
+          <t>evaluado_en</t>
+        </is>
+      </c>
+      <c r="D318" s="23" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="E318" s="24" t="n"/>
+      <c r="F318" s="25" t="inlineStr">
+        <is>
+          <t>Fecha y hora de la evaluación</t>
+        </is>
+      </c>
+      <c r="G318" s="25" t="inlineStr">
+        <is>
+          <t>Obligatorio. Por defecto clock_timestamp()</t>
+        </is>
+      </c>
+      <c r="H318" s="26" t="n"/>
+      <c r="I318" s="26" t="n"/>
+      <c r="J318" s="26" t="n"/>
+      <c r="K318" s="27" t="n"/>
+    </row>
+    <row r="320">
+      <c r="B320" s="5" t="inlineStr">
+        <is>
+          <t>resultado_criterio</t>
+        </is>
+      </c>
+      <c r="C320" s="6" t="n"/>
+      <c r="D320" s="6" t="n"/>
+      <c r="E320" s="6" t="n"/>
+      <c r="F320" s="6" t="n"/>
+      <c r="G320" s="6" t="n"/>
+      <c r="H320" s="6" t="n"/>
+      <c r="I320" s="6" t="n"/>
+      <c r="J320" s="6" t="n"/>
+      <c r="K320" s="7" t="n"/>
+    </row>
+    <row r="321" ht="15.75" customHeight="1">
+      <c r="B321" s="8" t="inlineStr">
+        <is>
+          <t>Resultado explicable de cada criterio (pilar) dentro de una evaluación.</t>
+        </is>
+      </c>
+      <c r="C321" s="9" t="n"/>
+      <c r="D321" s="9" t="n"/>
+      <c r="E321" s="9" t="n"/>
+      <c r="F321" s="9" t="n"/>
+      <c r="G321" s="9" t="n"/>
+      <c r="H321" s="9" t="n"/>
+      <c r="I321" s="9" t="n"/>
+      <c r="J321" s="9" t="n"/>
+      <c r="K321" s="10" t="n"/>
+    </row>
+    <row r="322">
+      <c r="B322" s="11" t="inlineStr">
+        <is>
+          <t>Tipo de Llave</t>
+        </is>
+      </c>
+      <c r="C322" s="12" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="D322" s="12" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="E322" s="12" t="inlineStr">
+        <is>
+          <t>Tamaño</t>
+        </is>
+      </c>
+      <c r="F322" s="12" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="G322" s="12" t="inlineStr">
+        <is>
+          <t>Observación</t>
+        </is>
+      </c>
+      <c r="H322" s="13" t="n"/>
+      <c r="I322" s="13" t="n"/>
+      <c r="J322" s="13" t="n"/>
+      <c r="K322" s="14" t="n"/>
+    </row>
+    <row r="323" ht="15.75" customHeight="1">
+      <c r="B323" s="15" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C323" s="16" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D323" s="16" t="inlineStr">
+        <is>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="E323" s="17" t="n"/>
+      <c r="F323" s="18" t="inlineStr">
+        <is>
+          <t>Identificador del resultado</t>
+        </is>
+      </c>
+      <c r="G323" s="18" t="inlineStr">
+        <is>
+          <t>Identity</t>
+        </is>
+      </c>
+      <c r="H323" s="19" t="n"/>
+      <c r="I323" s="19" t="n"/>
+      <c r="J323" s="19" t="n"/>
+      <c r="K323" s="20" t="n"/>
+    </row>
+    <row r="324" ht="15.75" customHeight="1">
+      <c r="B324" s="28" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="C324" s="16" t="inlineStr">
+        <is>
+          <t>evaluacion_id</t>
+        </is>
+      </c>
+      <c r="D324" s="16" t="inlineStr">
+        <is>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="E324" s="17" t="n"/>
+      <c r="F324" s="18" t="inlineStr">
+        <is>
+          <t>Evaluación a la que pertenece</t>
+        </is>
+      </c>
+      <c r="G324" s="18" t="inlineStr">
+        <is>
+          <t>Obligatorio. Tabla evaluacion_filtro. ON DELETE RESTRICT</t>
+        </is>
+      </c>
+      <c r="H324" s="19" t="n"/>
+      <c r="I324" s="19" t="n"/>
+      <c r="J324" s="19" t="n"/>
+      <c r="K324" s="20" t="n"/>
+    </row>
+    <row r="325" ht="15.75" customHeight="1">
+      <c r="B325" s="21" t="inlineStr"/>
+      <c r="C325" s="16" t="inlineStr">
+        <is>
+          <t>codigo</t>
+        </is>
+      </c>
+      <c r="D325" s="16" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="E318" s="17" t="n"/>
-      <c r="F318" s="18" t="inlineStr">
-        <is>
-          <t>Motivo de la clasificación</t>
-        </is>
-      </c>
-      <c r="G318" s="18" t="inlineStr">
-        <is>
-          <t>Obligatorio</t>
-        </is>
-      </c>
-      <c r="H318" s="19" t="n"/>
-      <c r="I318" s="19" t="n"/>
-      <c r="J318" s="19" t="n"/>
-      <c r="K318" s="20" t="n"/>
-    </row>
-    <row r="319" ht="30" customHeight="1">
-      <c r="B319" s="21" t="inlineStr"/>
-      <c r="C319" s="16" t="inlineStr">
-        <is>
-          <t>entrada_evaluada</t>
-        </is>
-      </c>
-      <c r="D319" s="16" t="inlineStr">
-        <is>
-          <t>jsonb</t>
-        </is>
-      </c>
-      <c r="E319" s="17" t="n"/>
-      <c r="F319" s="18" t="inlineStr">
-        <is>
-          <t>Snapshot de los datos, ítems y referencias de documentos usados</t>
-        </is>
-      </c>
-      <c r="G319" s="18" t="inlineStr">
-        <is>
-          <t>Obligatorio. Permite explicar resultados históricos</t>
-        </is>
-      </c>
-      <c r="H319" s="19" t="n"/>
-      <c r="I319" s="19" t="n"/>
-      <c r="J319" s="19" t="n"/>
-      <c r="K319" s="20" t="n"/>
-    </row>
-    <row r="320" ht="15.75" customHeight="1">
-      <c r="B320" s="21" t="inlineStr"/>
-      <c r="C320" s="16" t="inlineStr">
-        <is>
-          <t>metadatos</t>
-        </is>
-      </c>
-      <c r="D320" s="16" t="inlineStr">
-        <is>
-          <t>jsonb</t>
-        </is>
-      </c>
-      <c r="E320" s="17" t="n"/>
-      <c r="F320" s="18" t="inlineStr">
-        <is>
-          <t>Información complementaria de la evaluación</t>
-        </is>
-      </c>
-      <c r="G320" s="18" t="inlineStr">
-        <is>
-          <t>Obligatorio. Por defecto '{}'</t>
-        </is>
-      </c>
-      <c r="H320" s="19" t="n"/>
-      <c r="I320" s="19" t="n"/>
-      <c r="J320" s="19" t="n"/>
-      <c r="K320" s="20" t="n"/>
-    </row>
-    <row r="321" ht="15.75" customHeight="1">
-      <c r="B321" s="22" t="inlineStr"/>
-      <c r="C321" s="23" t="inlineStr">
-        <is>
-          <t>evaluado_en</t>
-        </is>
-      </c>
-      <c r="D321" s="23" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="E321" s="24" t="n"/>
-      <c r="F321" s="25" t="inlineStr">
-        <is>
-          <t>Fecha y hora de la evaluación</t>
-        </is>
-      </c>
-      <c r="G321" s="25" t="inlineStr">
-        <is>
-          <t>Obligatorio. Por defecto clock_timestamp()</t>
-        </is>
-      </c>
-      <c r="H321" s="26" t="n"/>
-      <c r="I321" s="26" t="n"/>
-      <c r="J321" s="26" t="n"/>
-      <c r="K321" s="27" t="n"/>
-    </row>
-    <row r="323">
-      <c r="B323" s="5" t="inlineStr">
-        <is>
-          <t>resultado_criterio</t>
-        </is>
-      </c>
-      <c r="C323" s="6" t="n"/>
-      <c r="D323" s="6" t="n"/>
-      <c r="E323" s="6" t="n"/>
-      <c r="F323" s="6" t="n"/>
-      <c r="G323" s="6" t="n"/>
-      <c r="H323" s="6" t="n"/>
-      <c r="I323" s="6" t="n"/>
-      <c r="J323" s="6" t="n"/>
-      <c r="K323" s="7" t="n"/>
-    </row>
-    <row r="324" ht="15.75" customHeight="1">
-      <c r="B324" s="8" t="inlineStr">
-        <is>
-          <t>Resultado explicable de cada criterio (pilar) dentro de una evaluación.</t>
-        </is>
-      </c>
-      <c r="C324" s="9" t="n"/>
-      <c r="D324" s="9" t="n"/>
-      <c r="E324" s="9" t="n"/>
-      <c r="F324" s="9" t="n"/>
-      <c r="G324" s="9" t="n"/>
-      <c r="H324" s="9" t="n"/>
-      <c r="I324" s="9" t="n"/>
-      <c r="J324" s="9" t="n"/>
-      <c r="K324" s="10" t="n"/>
-    </row>
-    <row r="325">
-      <c r="B325" s="11" t="inlineStr">
-        <is>
-          <t>Tipo de Llave</t>
-        </is>
-      </c>
-      <c r="C325" s="12" t="inlineStr">
-        <is>
-          <t>Atributo</t>
-        </is>
-      </c>
-      <c r="D325" s="12" t="inlineStr">
-        <is>
-          <t>Tipo</t>
-        </is>
-      </c>
-      <c r="E325" s="12" t="inlineStr">
-        <is>
-          <t>Tamaño</t>
-        </is>
-      </c>
-      <c r="F325" s="12" t="inlineStr">
-        <is>
-          <t>Descripción</t>
-        </is>
-      </c>
-      <c r="G325" s="12" t="inlineStr">
-        <is>
-          <t>Observación</t>
-        </is>
-      </c>
-      <c r="H325" s="13" t="n"/>
-      <c r="I325" s="13" t="n"/>
-      <c r="J325" s="13" t="n"/>
-      <c r="K325" s="14" t="n"/>
+      <c r="E325" s="17" t="n"/>
+      <c r="F325" s="18" t="inlineStr">
+        <is>
+          <t>Código del criterio</t>
+        </is>
+      </c>
+      <c r="G325" s="18" t="inlineStr">
+        <is>
+          <t>Obligatorio. Único junto a evaluacion_id</t>
+        </is>
+      </c>
+      <c r="H325" s="19" t="n"/>
+      <c r="I325" s="19" t="n"/>
+      <c r="J325" s="19" t="n"/>
+      <c r="K325" s="20" t="n"/>
     </row>
     <row r="326" ht="15.75" customHeight="1">
-      <c r="B326" s="15" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+      <c r="B326" s="21" t="inlineStr"/>
       <c r="C326" s="16" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>nombre</t>
         </is>
       </c>
       <c r="D326" s="16" t="inlineStr">
         <is>
-          <t>bigint</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E326" s="17" t="n"/>
       <c r="F326" s="18" t="inlineStr">
         <is>
-          <t>Identificador del resultado</t>
+          <t>Nombre del criterio</t>
         </is>
       </c>
       <c r="G326" s="18" t="inlineStr">
         <is>
-          <t>Identity</t>
+          <t>Obligatorio</t>
         </is>
       </c>
       <c r="H326" s="19" t="n"/>
@@ -8596,30 +8594,26 @@
       <c r="K326" s="20" t="n"/>
     </row>
     <row r="327" ht="15.75" customHeight="1">
-      <c r="B327" s="28" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
+      <c r="B327" s="21" t="inlineStr"/>
       <c r="C327" s="16" t="inlineStr">
         <is>
-          <t>evaluacion_id</t>
+          <t>caracter</t>
         </is>
       </c>
       <c r="D327" s="16" t="inlineStr">
         <is>
-          <t>bigint</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E327" s="17" t="n"/>
       <c r="F327" s="18" t="inlineStr">
         <is>
-          <t>Evaluación a la que pertenece</t>
+          <t>Carácter del criterio</t>
         </is>
       </c>
       <c r="G327" s="18" t="inlineStr">
         <is>
-          <t>Obligatorio. Tabla evaluacion_filtro. ON DELETE RESTRICT</t>
+          <t>Obligatorio. obligatorio, preferencia</t>
         </is>
       </c>
       <c r="H327" s="19" t="n"/>
@@ -8631,7 +8625,7 @@
       <c r="B328" s="21" t="inlineStr"/>
       <c r="C328" s="16" t="inlineStr">
         <is>
-          <t>codigo</t>
+          <t>resultado</t>
         </is>
       </c>
       <c r="D328" s="16" t="inlineStr">
@@ -8642,12 +8636,12 @@
       <c r="E328" s="17" t="n"/>
       <c r="F328" s="18" t="inlineStr">
         <is>
-          <t>Código del criterio</t>
+          <t>Resultado del criterio</t>
         </is>
       </c>
       <c r="G328" s="18" t="inlineStr">
         <is>
-          <t>Obligatorio. Único junto a evaluacion_id</t>
+          <t>Obligatorio. cumple, no_cumple, sin_informacion, no_aplica</t>
         </is>
       </c>
       <c r="H328" s="19" t="n"/>
@@ -8659,7 +8653,7 @@
       <c r="B329" s="21" t="inlineStr"/>
       <c r="C329" s="16" t="inlineStr">
         <is>
-          <t>nombre</t>
+          <t>motivo</t>
         </is>
       </c>
       <c r="D329" s="16" t="inlineStr">
@@ -8670,7 +8664,7 @@
       <c r="E329" s="17" t="n"/>
       <c r="F329" s="18" t="inlineStr">
         <is>
-          <t>Nombre del criterio</t>
+          <t>Explicación del resultado</t>
         </is>
       </c>
       <c r="G329" s="18" t="inlineStr">
@@ -8687,25 +8681,21 @@
       <c r="B330" s="21" t="inlineStr"/>
       <c r="C330" s="16" t="inlineStr">
         <is>
-          <t>caracter</t>
+          <t>valor_esperado</t>
         </is>
       </c>
       <c r="D330" s="16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>jsonb</t>
         </is>
       </c>
       <c r="E330" s="17" t="n"/>
       <c r="F330" s="18" t="inlineStr">
         <is>
-          <t>Carácter del criterio</t>
-        </is>
-      </c>
-      <c r="G330" s="18" t="inlineStr">
-        <is>
-          <t>Obligatorio. obligatorio, preferencia</t>
-        </is>
-      </c>
+          <t>Valor esperado según el perfil</t>
+        </is>
+      </c>
+      <c r="G330" s="18" t="inlineStr"/>
       <c r="H330" s="19" t="n"/>
       <c r="I330" s="19" t="n"/>
       <c r="J330" s="19" t="n"/>
@@ -8715,227 +8705,235 @@
       <c r="B331" s="21" t="inlineStr"/>
       <c r="C331" s="16" t="inlineStr">
         <is>
-          <t>resultado</t>
+          <t>valor_observado</t>
         </is>
       </c>
       <c r="D331" s="16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>jsonb</t>
         </is>
       </c>
       <c r="E331" s="17" t="n"/>
       <c r="F331" s="18" t="inlineStr">
         <is>
-          <t>Resultado del criterio</t>
-        </is>
-      </c>
-      <c r="G331" s="18" t="inlineStr">
-        <is>
-          <t>Obligatorio. cumple, no_cumple, sin_informacion, no_aplica</t>
-        </is>
-      </c>
+          <t>Valor encontrado en la oportunidad</t>
+        </is>
+      </c>
+      <c r="G331" s="18" t="inlineStr"/>
       <c r="H331" s="19" t="n"/>
       <c r="I331" s="19" t="n"/>
       <c r="J331" s="19" t="n"/>
       <c r="K331" s="20" t="n"/>
     </row>
-    <row r="332" ht="15.75" customHeight="1">
-      <c r="B332" s="21" t="inlineStr"/>
-      <c r="C332" s="16" t="inlineStr">
-        <is>
-          <t>motivo</t>
-        </is>
-      </c>
-      <c r="D332" s="16" t="inlineStr">
+    <row r="332" ht="30" customHeight="1">
+      <c r="B332" s="22" t="inlineStr"/>
+      <c r="C332" s="23" t="inlineStr">
+        <is>
+          <t>evidencias</t>
+        </is>
+      </c>
+      <c r="D332" s="23" t="inlineStr">
+        <is>
+          <t>jsonb</t>
+        </is>
+      </c>
+      <c r="E332" s="24" t="n"/>
+      <c r="F332" s="25" t="inlineStr">
+        <is>
+          <t>Evidencias del resultado (documento, página y cita, o campo de la API)</t>
+        </is>
+      </c>
+      <c r="G332" s="25" t="inlineStr">
+        <is>
+          <t>Obligatorio. Por defecto '[]'</t>
+        </is>
+      </c>
+      <c r="H332" s="26" t="n"/>
+      <c r="I332" s="26" t="n"/>
+      <c r="J332" s="26" t="n"/>
+      <c r="K332" s="27" t="n"/>
+    </row>
+    <row r="334">
+      <c r="B334" s="5" t="inlineStr">
+        <is>
+          <t>revision_manual</t>
+        </is>
+      </c>
+      <c r="C334" s="6" t="n"/>
+      <c r="D334" s="6" t="n"/>
+      <c r="E334" s="6" t="n"/>
+      <c r="F334" s="6" t="n"/>
+      <c r="G334" s="6" t="n"/>
+      <c r="H334" s="6" t="n"/>
+      <c r="I334" s="6" t="n"/>
+      <c r="J334" s="6" t="n"/>
+      <c r="K334" s="7" t="n"/>
+    </row>
+    <row r="335" ht="15.75" customHeight="1">
+      <c r="B335" s="8" t="inlineStr">
+        <is>
+          <t>Corrección humana de una evaluación; prevalece sobre la propuesta automática.</t>
+        </is>
+      </c>
+      <c r="C335" s="9" t="n"/>
+      <c r="D335" s="9" t="n"/>
+      <c r="E335" s="9" t="n"/>
+      <c r="F335" s="9" t="n"/>
+      <c r="G335" s="9" t="n"/>
+      <c r="H335" s="9" t="n"/>
+      <c r="I335" s="9" t="n"/>
+      <c r="J335" s="9" t="n"/>
+      <c r="K335" s="10" t="n"/>
+    </row>
+    <row r="336">
+      <c r="B336" s="11" t="inlineStr">
+        <is>
+          <t>Tipo de Llave</t>
+        </is>
+      </c>
+      <c r="C336" s="12" t="inlineStr">
+        <is>
+          <t>Atributo</t>
+        </is>
+      </c>
+      <c r="D336" s="12" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="E336" s="12" t="inlineStr">
+        <is>
+          <t>Tamaño</t>
+        </is>
+      </c>
+      <c r="F336" s="12" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="G336" s="12" t="inlineStr">
+        <is>
+          <t>Observación</t>
+        </is>
+      </c>
+      <c r="H336" s="13" t="n"/>
+      <c r="I336" s="13" t="n"/>
+      <c r="J336" s="13" t="n"/>
+      <c r="K336" s="14" t="n"/>
+    </row>
+    <row r="337" ht="15.75" customHeight="1">
+      <c r="B337" s="15" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="C337" s="16" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D337" s="16" t="inlineStr">
+        <is>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="E337" s="17" t="n"/>
+      <c r="F337" s="18" t="inlineStr">
+        <is>
+          <t>Identificador de la revisión</t>
+        </is>
+      </c>
+      <c r="G337" s="18" t="inlineStr">
+        <is>
+          <t>Identity</t>
+        </is>
+      </c>
+      <c r="H337" s="19" t="n"/>
+      <c r="I337" s="19" t="n"/>
+      <c r="J337" s="19" t="n"/>
+      <c r="K337" s="20" t="n"/>
+    </row>
+    <row r="338" ht="15.75" customHeight="1">
+      <c r="B338" s="28" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="C338" s="16" t="inlineStr">
+        <is>
+          <t>evaluacion_id</t>
+        </is>
+      </c>
+      <c r="D338" s="16" t="inlineStr">
+        <is>
+          <t>bigint</t>
+        </is>
+      </c>
+      <c r="E338" s="17" t="n"/>
+      <c r="F338" s="18" t="inlineStr">
+        <is>
+          <t>Evaluación revisada</t>
+        </is>
+      </c>
+      <c r="G338" s="18" t="inlineStr">
+        <is>
+          <t>Obligatorio. Tabla evaluacion_filtro. ON DELETE RESTRICT</t>
+        </is>
+      </c>
+      <c r="H338" s="19" t="n"/>
+      <c r="I338" s="19" t="n"/>
+      <c r="J338" s="19" t="n"/>
+      <c r="K338" s="20" t="n"/>
+    </row>
+    <row r="339" ht="15.75" customHeight="1">
+      <c r="B339" s="21" t="inlineStr"/>
+      <c r="C339" s="16" t="inlineStr">
+        <is>
+          <t>accion</t>
+        </is>
+      </c>
+      <c r="D339" s="16" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="E332" s="17" t="n"/>
-      <c r="F332" s="18" t="inlineStr">
-        <is>
-          <t>Explicación del resultado</t>
-        </is>
-      </c>
-      <c r="G332" s="18" t="inlineStr">
-        <is>
-          <t>Obligatorio</t>
-        </is>
-      </c>
-      <c r="H332" s="19" t="n"/>
-      <c r="I332" s="19" t="n"/>
-      <c r="J332" s="19" t="n"/>
-      <c r="K332" s="20" t="n"/>
-    </row>
-    <row r="333" ht="15.75" customHeight="1">
-      <c r="B333" s="21" t="inlineStr"/>
-      <c r="C333" s="16" t="inlineStr">
-        <is>
-          <t>valor_esperado</t>
-        </is>
-      </c>
-      <c r="D333" s="16" t="inlineStr">
-        <is>
-          <t>jsonb</t>
-        </is>
-      </c>
-      <c r="E333" s="17" t="n"/>
-      <c r="F333" s="18" t="inlineStr">
-        <is>
-          <t>Valor esperado según el perfil</t>
-        </is>
-      </c>
-      <c r="G333" s="18" t="inlineStr"/>
-      <c r="H333" s="19" t="n"/>
-      <c r="I333" s="19" t="n"/>
-      <c r="J333" s="19" t="n"/>
-      <c r="K333" s="20" t="n"/>
-    </row>
-    <row r="334" ht="15.75" customHeight="1">
-      <c r="B334" s="21" t="inlineStr"/>
-      <c r="C334" s="16" t="inlineStr">
-        <is>
-          <t>valor_observado</t>
-        </is>
-      </c>
-      <c r="D334" s="16" t="inlineStr">
-        <is>
-          <t>jsonb</t>
-        </is>
-      </c>
-      <c r="E334" s="17" t="n"/>
-      <c r="F334" s="18" t="inlineStr">
-        <is>
-          <t>Valor encontrado en la oportunidad</t>
-        </is>
-      </c>
-      <c r="G334" s="18" t="inlineStr"/>
-      <c r="H334" s="19" t="n"/>
-      <c r="I334" s="19" t="n"/>
-      <c r="J334" s="19" t="n"/>
-      <c r="K334" s="20" t="n"/>
-    </row>
-    <row r="335" ht="30" customHeight="1">
-      <c r="B335" s="22" t="inlineStr"/>
-      <c r="C335" s="23" t="inlineStr">
-        <is>
-          <t>evidencias</t>
-        </is>
-      </c>
-      <c r="D335" s="23" t="inlineStr">
-        <is>
-          <t>jsonb</t>
-        </is>
-      </c>
-      <c r="E335" s="24" t="n"/>
-      <c r="F335" s="25" t="inlineStr">
-        <is>
-          <t>Evidencias del resultado (documento, página y cita, o campo de la API)</t>
-        </is>
-      </c>
-      <c r="G335" s="25" t="inlineStr">
-        <is>
-          <t>Obligatorio. Por defecto '[]'</t>
-        </is>
-      </c>
-      <c r="H335" s="26" t="n"/>
-      <c r="I335" s="26" t="n"/>
-      <c r="J335" s="26" t="n"/>
-      <c r="K335" s="27" t="n"/>
-    </row>
-    <row r="337">
-      <c r="B337" s="5" t="inlineStr">
-        <is>
-          <t>revision_manual</t>
-        </is>
-      </c>
-      <c r="C337" s="6" t="n"/>
-      <c r="D337" s="6" t="n"/>
-      <c r="E337" s="6" t="n"/>
-      <c r="F337" s="6" t="n"/>
-      <c r="G337" s="6" t="n"/>
-      <c r="H337" s="6" t="n"/>
-      <c r="I337" s="6" t="n"/>
-      <c r="J337" s="6" t="n"/>
-      <c r="K337" s="7" t="n"/>
-    </row>
-    <row r="338" ht="15.75" customHeight="1">
-      <c r="B338" s="8" t="inlineStr">
-        <is>
-          <t>Corrección humana de una evaluación; prevalece sobre la propuesta automática.</t>
-        </is>
-      </c>
-      <c r="C338" s="9" t="n"/>
-      <c r="D338" s="9" t="n"/>
-      <c r="E338" s="9" t="n"/>
-      <c r="F338" s="9" t="n"/>
-      <c r="G338" s="9" t="n"/>
-      <c r="H338" s="9" t="n"/>
-      <c r="I338" s="9" t="n"/>
-      <c r="J338" s="9" t="n"/>
-      <c r="K338" s="10" t="n"/>
-    </row>
-    <row r="339">
-      <c r="B339" s="11" t="inlineStr">
-        <is>
-          <t>Tipo de Llave</t>
-        </is>
-      </c>
-      <c r="C339" s="12" t="inlineStr">
-        <is>
-          <t>Atributo</t>
-        </is>
-      </c>
-      <c r="D339" s="12" t="inlineStr">
-        <is>
-          <t>Tipo</t>
-        </is>
-      </c>
-      <c r="E339" s="12" t="inlineStr">
-        <is>
-          <t>Tamaño</t>
-        </is>
-      </c>
-      <c r="F339" s="12" t="inlineStr">
-        <is>
-          <t>Descripción</t>
-        </is>
-      </c>
-      <c r="G339" s="12" t="inlineStr">
-        <is>
-          <t>Observación</t>
-        </is>
-      </c>
-      <c r="H339" s="13" t="n"/>
-      <c r="I339" s="13" t="n"/>
-      <c r="J339" s="13" t="n"/>
-      <c r="K339" s="14" t="n"/>
-    </row>
-    <row r="340" ht="15.75" customHeight="1">
-      <c r="B340" s="15" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
+      <c r="E339" s="17" t="n"/>
+      <c r="F339" s="18" t="inlineStr">
+        <is>
+          <t>Acción decidida por el revisor</t>
+        </is>
+      </c>
+      <c r="G339" s="18" t="inlineStr">
+        <is>
+          <t>Obligatorio. confirmar_relevante, descartar, mantener_pendiente</t>
+        </is>
+      </c>
+      <c r="H339" s="19" t="n"/>
+      <c r="I339" s="19" t="n"/>
+      <c r="J339" s="19" t="n"/>
+      <c r="K339" s="20" t="n"/>
+    </row>
+    <row r="340" ht="30" customHeight="1">
+      <c r="B340" s="21" t="inlineStr"/>
       <c r="C340" s="16" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>relevancia_confirmada</t>
         </is>
       </c>
       <c r="D340" s="16" t="inlineStr">
         <is>
-          <t>bigint</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E340" s="17" t="n"/>
       <c r="F340" s="18" t="inlineStr">
         <is>
-          <t>Identificador de la revisión</t>
+          <t>Relevancia confirmada por el revisor</t>
         </is>
       </c>
       <c r="G340" s="18" t="inlineStr">
         <is>
-          <t>Identity</t>
+          <t>Obligatorio. relevante, no_relevante, sin_determinar (por defecto)</t>
         </is>
       </c>
       <c r="H340" s="19" t="n"/>
@@ -8943,31 +8941,27 @@
       <c r="J340" s="19" t="n"/>
       <c r="K340" s="20" t="n"/>
     </row>
-    <row r="341" ht="15.75" customHeight="1">
-      <c r="B341" s="28" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
+    <row r="341" ht="30" customHeight="1">
+      <c r="B341" s="21" t="inlineStr"/>
       <c r="C341" s="16" t="inlineStr">
         <is>
-          <t>evaluacion_id</t>
+          <t>categoria_motivo</t>
         </is>
       </c>
       <c r="D341" s="16" t="inlineStr">
         <is>
-          <t>bigint</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E341" s="17" t="n"/>
       <c r="F341" s="18" t="inlineStr">
         <is>
-          <t>Evaluación revisada</t>
+          <t>Categoría del motivo</t>
         </is>
       </c>
       <c r="G341" s="18" t="inlineStr">
         <is>
-          <t>Obligatorio. Tabla evaluacion_filtro. ON DELETE RESTRICT</t>
+          <t>Obligatorio. servicio, capacidad, ubicacion, plazo, documentos, presupuesto, otro</t>
         </is>
       </c>
       <c r="H341" s="19" t="n"/>
@@ -8975,11 +8969,11 @@
       <c r="J341" s="19" t="n"/>
       <c r="K341" s="20" t="n"/>
     </row>
-    <row r="342" ht="30" customHeight="1">
+    <row r="342" ht="15.75" customHeight="1">
       <c r="B342" s="21" t="inlineStr"/>
       <c r="C342" s="16" t="inlineStr">
         <is>
-          <t>accion</t>
+          <t>motivo</t>
         </is>
       </c>
       <c r="D342" s="16" t="inlineStr">
@@ -8990,12 +8984,12 @@
       <c r="E342" s="17" t="n"/>
       <c r="F342" s="18" t="inlineStr">
         <is>
-          <t>Acción decidida por el revisor</t>
+          <t>Motivo de la revisión</t>
         </is>
       </c>
       <c r="G342" s="18" t="inlineStr">
         <is>
-          <t>Obligatorio. enviar_a_llm, confirmar_relevante, descartar, mantener_pendiente</t>
+          <t>Obligatorio</t>
         </is>
       </c>
       <c r="H342" s="19" t="n"/>
@@ -9004,26 +8998,30 @@
       <c r="K342" s="20" t="n"/>
     </row>
     <row r="343" ht="30" customHeight="1">
-      <c r="B343" s="21" t="inlineStr"/>
+      <c r="B343" s="28" t="inlineStr">
+        <is>
+          <t>FK lógica</t>
+        </is>
+      </c>
       <c r="C343" s="16" t="inlineStr">
         <is>
-          <t>relevancia_confirmada</t>
+          <t>revisado_por</t>
         </is>
       </c>
       <c r="D343" s="16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>uuid</t>
         </is>
       </c>
       <c r="E343" s="17" t="n"/>
       <c r="F343" s="18" t="inlineStr">
         <is>
-          <t>Relevancia confirmada por el revisor</t>
+          <t>Usuario que realizó la revisión</t>
         </is>
       </c>
       <c r="G343" s="18" t="inlineStr">
         <is>
-          <t>Obligatorio. relevante, no_relevante, sin_determinar (por defecto)</t>
+          <t>Obligatorio. usuario.id de Usuarios/Licitaciones. Se toma de la sesión validada</t>
         </is>
       </c>
       <c r="H343" s="19" t="n"/>
@@ -9031,631 +9029,46 @@
       <c r="J343" s="19" t="n"/>
       <c r="K343" s="20" t="n"/>
     </row>
-    <row r="344" ht="30" customHeight="1">
-      <c r="B344" s="21" t="inlineStr"/>
-      <c r="C344" s="16" t="inlineStr">
-        <is>
-          <t>categoria_motivo</t>
-        </is>
-      </c>
-      <c r="D344" s="16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E344" s="17" t="n"/>
-      <c r="F344" s="18" t="inlineStr">
-        <is>
-          <t>Categoría del motivo</t>
-        </is>
-      </c>
-      <c r="G344" s="18" t="inlineStr">
-        <is>
-          <t>Obligatorio. servicio, capacidad, ubicacion, plazo, documentos, presupuesto, otro</t>
-        </is>
-      </c>
-      <c r="H344" s="19" t="n"/>
-      <c r="I344" s="19" t="n"/>
-      <c r="J344" s="19" t="n"/>
-      <c r="K344" s="20" t="n"/>
-    </row>
-    <row r="345" ht="15.75" customHeight="1">
-      <c r="B345" s="21" t="inlineStr"/>
-      <c r="C345" s="16" t="inlineStr">
-        <is>
-          <t>motivo</t>
-        </is>
-      </c>
-      <c r="D345" s="16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E345" s="17" t="n"/>
-      <c r="F345" s="18" t="inlineStr">
-        <is>
-          <t>Motivo de la revisión</t>
-        </is>
-      </c>
-      <c r="G345" s="18" t="inlineStr">
-        <is>
-          <t>Obligatorio</t>
-        </is>
-      </c>
-      <c r="H345" s="19" t="n"/>
-      <c r="I345" s="19" t="n"/>
-      <c r="J345" s="19" t="n"/>
-      <c r="K345" s="20" t="n"/>
-    </row>
-    <row r="346" ht="30" customHeight="1">
-      <c r="B346" s="28" t="inlineStr">
-        <is>
-          <t>FK lógica</t>
-        </is>
-      </c>
-      <c r="C346" s="16" t="inlineStr">
-        <is>
-          <t>revisado_por</t>
-        </is>
-      </c>
-      <c r="D346" s="16" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="E346" s="17" t="n"/>
-      <c r="F346" s="18" t="inlineStr">
-        <is>
-          <t>Usuario que realizó la revisión</t>
-        </is>
-      </c>
-      <c r="G346" s="18" t="inlineStr">
-        <is>
-          <t>Obligatorio. usuario.id de Usuarios/Licitaciones. Se toma de la sesión validada</t>
-        </is>
-      </c>
-      <c r="H346" s="19" t="n"/>
-      <c r="I346" s="19" t="n"/>
-      <c r="J346" s="19" t="n"/>
-      <c r="K346" s="20" t="n"/>
-    </row>
-    <row r="347" ht="15.75" customHeight="1">
-      <c r="B347" s="22" t="inlineStr"/>
-      <c r="C347" s="23" t="inlineStr">
+    <row r="344" ht="15.75" customHeight="1">
+      <c r="B344" s="22" t="inlineStr"/>
+      <c r="C344" s="23" t="inlineStr">
         <is>
           <t>revisado_en</t>
         </is>
       </c>
-      <c r="D347" s="23" t="inlineStr">
+      <c r="D344" s="23" t="inlineStr">
         <is>
           <t>timestamptz</t>
         </is>
       </c>
-      <c r="E347" s="24" t="n"/>
-      <c r="F347" s="25" t="inlineStr">
+      <c r="E344" s="24" t="n"/>
+      <c r="F344" s="25" t="inlineStr">
         <is>
           <t>Fecha y hora de la revisión</t>
         </is>
       </c>
-      <c r="G347" s="25" t="inlineStr">
+      <c r="G344" s="25" t="inlineStr">
         <is>
           <t>Obligatorio. Por defecto clock_timestamp()</t>
         </is>
       </c>
-      <c r="H347" s="26" t="n"/>
-      <c r="I347" s="26" t="n"/>
-      <c r="J347" s="26" t="n"/>
-      <c r="K347" s="27" t="n"/>
-    </row>
-    <row r="349">
-      <c r="B349" s="5" t="inlineStr">
-        <is>
-          <t>analisis_llm</t>
-        </is>
-      </c>
-      <c r="C349" s="6" t="n"/>
-      <c r="D349" s="6" t="n"/>
-      <c r="E349" s="6" t="n"/>
-      <c r="F349" s="6" t="n"/>
-      <c r="G349" s="6" t="n"/>
-      <c r="H349" s="6" t="n"/>
-      <c r="I349" s="6" t="n"/>
-      <c r="J349" s="6" t="n"/>
-      <c r="K349" s="7" t="n"/>
-    </row>
-    <row r="350" ht="15.75" customHeight="1">
-      <c r="B350" s="8" t="inlineStr">
-        <is>
-          <t>Solicitud y resultado del análisis de una oportunidad con un modelo de lenguaje (LLM). La tabla no ejecuta IA automáticamente.</t>
-        </is>
-      </c>
-      <c r="C350" s="9" t="n"/>
-      <c r="D350" s="9" t="n"/>
-      <c r="E350" s="9" t="n"/>
-      <c r="F350" s="9" t="n"/>
-      <c r="G350" s="9" t="n"/>
-      <c r="H350" s="9" t="n"/>
-      <c r="I350" s="9" t="n"/>
-      <c r="J350" s="9" t="n"/>
-      <c r="K350" s="10" t="n"/>
-    </row>
-    <row r="351">
-      <c r="B351" s="11" t="inlineStr">
-        <is>
-          <t>Tipo de Llave</t>
-        </is>
-      </c>
-      <c r="C351" s="12" t="inlineStr">
-        <is>
-          <t>Atributo</t>
-        </is>
-      </c>
-      <c r="D351" s="12" t="inlineStr">
-        <is>
-          <t>Tipo</t>
-        </is>
-      </c>
-      <c r="E351" s="12" t="inlineStr">
-        <is>
-          <t>Tamaño</t>
-        </is>
-      </c>
-      <c r="F351" s="12" t="inlineStr">
-        <is>
-          <t>Descripción</t>
-        </is>
-      </c>
-      <c r="G351" s="12" t="inlineStr">
-        <is>
-          <t>Observación</t>
-        </is>
-      </c>
-      <c r="H351" s="13" t="n"/>
-      <c r="I351" s="13" t="n"/>
-      <c r="J351" s="13" t="n"/>
-      <c r="K351" s="14" t="n"/>
-    </row>
-    <row r="352" ht="15.75" customHeight="1">
-      <c r="B352" s="15" t="inlineStr">
-        <is>
-          <t>PK</t>
-        </is>
-      </c>
-      <c r="C352" s="16" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D352" s="16" t="inlineStr">
-        <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="E352" s="17" t="n"/>
-      <c r="F352" s="18" t="inlineStr">
-        <is>
-          <t>Identificador del análisis</t>
-        </is>
-      </c>
-      <c r="G352" s="18" t="inlineStr">
-        <is>
-          <t>Identity</t>
-        </is>
-      </c>
-      <c r="H352" s="19" t="n"/>
-      <c r="I352" s="19" t="n"/>
-      <c r="J352" s="19" t="n"/>
-      <c r="K352" s="20" t="n"/>
-    </row>
-    <row r="353" ht="15.75" customHeight="1">
-      <c r="B353" s="28" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="C353" s="16" t="inlineStr">
-        <is>
-          <t>evaluacion_id</t>
-        </is>
-      </c>
-      <c r="D353" s="16" t="inlineStr">
-        <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="E353" s="17" t="n"/>
-      <c r="F353" s="18" t="inlineStr">
-        <is>
-          <t>Evaluación analizada</t>
-        </is>
-      </c>
-      <c r="G353" s="18" t="inlineStr">
-        <is>
-          <t>Obligatorio. Tabla evaluacion_filtro. ON DELETE RESTRICT</t>
-        </is>
-      </c>
-      <c r="H353" s="19" t="n"/>
-      <c r="I353" s="19" t="n"/>
-      <c r="J353" s="19" t="n"/>
-      <c r="K353" s="20" t="n"/>
-    </row>
-    <row r="354" ht="15.75" customHeight="1">
-      <c r="B354" s="28" t="inlineStr">
-        <is>
-          <t>FK</t>
-        </is>
-      </c>
-      <c r="C354" s="16" t="inlineStr">
-        <is>
-          <t>revision_id</t>
-        </is>
-      </c>
-      <c r="D354" s="16" t="inlineStr">
-        <is>
-          <t>bigint</t>
-        </is>
-      </c>
-      <c r="E354" s="17" t="n"/>
-      <c r="F354" s="18" t="inlineStr">
-        <is>
-          <t>Revisión manual que originó la solicitud</t>
-        </is>
-      </c>
-      <c r="G354" s="18" t="inlineStr">
-        <is>
-          <t>FK compuesta (revision_id, evaluacion_id) a revision_manual</t>
-        </is>
-      </c>
-      <c r="H354" s="19" t="n"/>
-      <c r="I354" s="19" t="n"/>
-      <c r="J354" s="19" t="n"/>
-      <c r="K354" s="20" t="n"/>
-    </row>
-    <row r="355" ht="15.75" customHeight="1">
-      <c r="B355" s="21" t="inlineStr"/>
-      <c r="C355" s="16" t="inlineStr">
-        <is>
-          <t>solicitud_id</t>
-        </is>
-      </c>
-      <c r="D355" s="16" t="inlineStr">
-        <is>
-          <t>uuid</t>
-        </is>
-      </c>
-      <c r="E355" s="17" t="n"/>
-      <c r="F355" s="18" t="inlineStr">
-        <is>
-          <t>Clave de idempotencia de la solicitud</t>
-        </is>
-      </c>
-      <c r="G355" s="18" t="inlineStr">
-        <is>
-          <t>Obligatorio. Valor único</t>
-        </is>
-      </c>
-      <c r="H355" s="19" t="n"/>
-      <c r="I355" s="19" t="n"/>
-      <c r="J355" s="19" t="n"/>
-      <c r="K355" s="20" t="n"/>
-    </row>
-    <row r="356" ht="30" customHeight="1">
-      <c r="B356" s="21" t="inlineStr"/>
-      <c r="C356" s="16" t="inlineStr">
-        <is>
-          <t>estado</t>
-        </is>
-      </c>
-      <c r="D356" s="16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E356" s="17" t="n"/>
-      <c r="F356" s="18" t="inlineStr">
-        <is>
-          <t>Estado del análisis</t>
-        </is>
-      </c>
-      <c r="G356" s="18" t="inlineStr">
-        <is>
-          <t>Obligatorio. pendiente (por defecto), procesando, completado, error</t>
-        </is>
-      </c>
-      <c r="H356" s="19" t="n"/>
-      <c r="I356" s="19" t="n"/>
-      <c r="J356" s="19" t="n"/>
-      <c r="K356" s="20" t="n"/>
-    </row>
-    <row r="357" ht="15.75" customHeight="1">
-      <c r="B357" s="21" t="inlineStr"/>
-      <c r="C357" s="16" t="inlineStr">
-        <is>
-          <t>proveedor</t>
-        </is>
-      </c>
-      <c r="D357" s="16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E357" s="17" t="n"/>
-      <c r="F357" s="18" t="inlineStr">
-        <is>
-          <t>Proveedor del LLM</t>
-        </is>
-      </c>
-      <c r="G357" s="18" t="inlineStr">
-        <is>
-          <t>Obligatorio si está completado</t>
-        </is>
-      </c>
-      <c r="H357" s="19" t="n"/>
-      <c r="I357" s="19" t="n"/>
-      <c r="J357" s="19" t="n"/>
-      <c r="K357" s="20" t="n"/>
-    </row>
-    <row r="358" ht="15.75" customHeight="1">
-      <c r="B358" s="21" t="inlineStr"/>
-      <c r="C358" s="16" t="inlineStr">
-        <is>
-          <t>modelo</t>
-        </is>
-      </c>
-      <c r="D358" s="16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E358" s="17" t="n"/>
-      <c r="F358" s="18" t="inlineStr">
-        <is>
-          <t>Modelo de lenguaje usado</t>
-        </is>
-      </c>
-      <c r="G358" s="18" t="inlineStr">
-        <is>
-          <t>Obligatorio si está completado</t>
-        </is>
-      </c>
-      <c r="H358" s="19" t="n"/>
-      <c r="I358" s="19" t="n"/>
-      <c r="J358" s="19" t="n"/>
-      <c r="K358" s="20" t="n"/>
-    </row>
-    <row r="359" ht="15.75" customHeight="1">
-      <c r="B359" s="21" t="inlineStr"/>
-      <c r="C359" s="16" t="inlineStr">
-        <is>
-          <t>version_prompt</t>
-        </is>
-      </c>
-      <c r="D359" s="16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E359" s="17" t="n"/>
-      <c r="F359" s="18" t="inlineStr">
-        <is>
-          <t>Versión del prompt</t>
-        </is>
-      </c>
-      <c r="G359" s="18" t="inlineStr">
-        <is>
-          <t>Obligatorio si está completado</t>
-        </is>
-      </c>
-      <c r="H359" s="19" t="n"/>
-      <c r="I359" s="19" t="n"/>
-      <c r="J359" s="19" t="n"/>
-      <c r="K359" s="20" t="n"/>
-    </row>
-    <row r="360" ht="15.75" customHeight="1">
-      <c r="B360" s="21" t="inlineStr"/>
-      <c r="C360" s="16" t="inlineStr">
-        <is>
-          <t>resumen</t>
-        </is>
-      </c>
-      <c r="D360" s="16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E360" s="17" t="n"/>
-      <c r="F360" s="18" t="inlineStr">
-        <is>
-          <t>Resumen del análisis</t>
-        </is>
-      </c>
-      <c r="G360" s="18" t="inlineStr">
-        <is>
-          <t>Obligatorio si está completado</t>
-        </is>
-      </c>
-      <c r="H360" s="19" t="n"/>
-      <c r="I360" s="19" t="n"/>
-      <c r="J360" s="19" t="n"/>
-      <c r="K360" s="20" t="n"/>
-    </row>
-    <row r="361" ht="30" customHeight="1">
-      <c r="B361" s="21" t="inlineStr"/>
-      <c r="C361" s="16" t="inlineStr">
-        <is>
-          <t>salida_estructurada</t>
-        </is>
-      </c>
-      <c r="D361" s="16" t="inlineStr">
-        <is>
-          <t>jsonb</t>
-        </is>
-      </c>
-      <c r="E361" s="17" t="n"/>
-      <c r="F361" s="18" t="inlineStr">
-        <is>
-          <t>Salida versionada: servicios, requisitos, documentos, fechas, criterios y evidencias</t>
-        </is>
-      </c>
-      <c r="G361" s="18" t="inlineStr">
-        <is>
-          <t>No es una decisión de participar</t>
-        </is>
-      </c>
-      <c r="H361" s="19" t="n"/>
-      <c r="I361" s="19" t="n"/>
-      <c r="J361" s="19" t="n"/>
-      <c r="K361" s="20" t="n"/>
-    </row>
-    <row r="362" ht="15.75" customHeight="1">
-      <c r="B362" s="21" t="inlineStr"/>
-      <c r="C362" s="16" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="D362" s="16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E362" s="17" t="n"/>
-      <c r="F362" s="18" t="inlineStr">
-        <is>
-          <t>Mensaje de error</t>
-        </is>
-      </c>
-      <c r="G362" s="18" t="inlineStr">
-        <is>
-          <t>Obligatorio si estado = error</t>
-        </is>
-      </c>
-      <c r="H362" s="19" t="n"/>
-      <c r="I362" s="19" t="n"/>
-      <c r="J362" s="19" t="n"/>
-      <c r="K362" s="20" t="n"/>
-    </row>
-    <row r="363" ht="15.75" customHeight="1">
-      <c r="B363" s="21" t="inlineStr"/>
-      <c r="C363" s="16" t="inlineStr">
-        <is>
-          <t>intentos</t>
-        </is>
-      </c>
-      <c r="D363" s="16" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="E363" s="17" t="n"/>
-      <c r="F363" s="18" t="inlineStr">
-        <is>
-          <t>Cantidad de intentos</t>
-        </is>
-      </c>
-      <c r="G363" s="18" t="inlineStr">
-        <is>
-          <t>Obligatorio. Por defecto 0</t>
-        </is>
-      </c>
-      <c r="H363" s="19" t="n"/>
-      <c r="I363" s="19" t="n"/>
-      <c r="J363" s="19" t="n"/>
-      <c r="K363" s="20" t="n"/>
-    </row>
-    <row r="364" ht="15.75" customHeight="1">
-      <c r="B364" s="21" t="inlineStr"/>
-      <c r="C364" s="16" t="inlineStr">
-        <is>
-          <t>solicitado_en</t>
-        </is>
-      </c>
-      <c r="D364" s="16" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="E364" s="17" t="n"/>
-      <c r="F364" s="18" t="inlineStr">
-        <is>
-          <t>Fecha de la solicitud</t>
-        </is>
-      </c>
-      <c r="G364" s="18" t="inlineStr">
-        <is>
-          <t>Obligatorio. Por defecto clock_timestamp()</t>
-        </is>
-      </c>
-      <c r="H364" s="19" t="n"/>
-      <c r="I364" s="19" t="n"/>
-      <c r="J364" s="19" t="n"/>
-      <c r="K364" s="20" t="n"/>
-    </row>
-    <row r="365" ht="15.75" customHeight="1">
-      <c r="B365" s="21" t="inlineStr"/>
-      <c r="C365" s="16" t="inlineStr">
-        <is>
-          <t>iniciado_en</t>
-        </is>
-      </c>
-      <c r="D365" s="16" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="E365" s="17" t="n"/>
-      <c r="F365" s="18" t="inlineStr">
-        <is>
-          <t>Inicio del procesamiento</t>
-        </is>
-      </c>
-      <c r="G365" s="18" t="inlineStr"/>
-      <c r="H365" s="19" t="n"/>
-      <c r="I365" s="19" t="n"/>
-      <c r="J365" s="19" t="n"/>
-      <c r="K365" s="20" t="n"/>
-    </row>
-    <row r="366" ht="15.75" customHeight="1">
-      <c r="B366" s="22" t="inlineStr"/>
-      <c r="C366" s="23" t="inlineStr">
-        <is>
-          <t>finalizado_en</t>
-        </is>
-      </c>
-      <c r="D366" s="23" t="inlineStr">
-        <is>
-          <t>timestamptz</t>
-        </is>
-      </c>
-      <c r="E366" s="24" t="n"/>
-      <c r="F366" s="25" t="inlineStr">
-        <is>
-          <t>Término del procesamiento</t>
-        </is>
-      </c>
-      <c r="G366" s="25" t="inlineStr">
-        <is>
-          <t>Mayor o igual a iniciado_en</t>
-        </is>
-      </c>
-      <c r="H366" s="26" t="n"/>
-      <c r="I366" s="26" t="n"/>
-      <c r="J366" s="26" t="n"/>
-      <c r="K366" s="27" t="n"/>
+      <c r="H344" s="26" t="n"/>
+      <c r="I344" s="26" t="n"/>
+      <c r="J344" s="26" t="n"/>
+      <c r="K344" s="27" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="340">
+  <mergeCells count="319">
     <mergeCell ref="G12:K12"/>
     <mergeCell ref="B6:K6"/>
-    <mergeCell ref="G362:K362"/>
     <mergeCell ref="G39:K39"/>
     <mergeCell ref="G70:K70"/>
     <mergeCell ref="B198:K198"/>
     <mergeCell ref="G312:K312"/>
+    <mergeCell ref="G337:K337"/>
     <mergeCell ref="B160:K160"/>
     <mergeCell ref="G116:K116"/>
     <mergeCell ref="B4:K4"/>
-    <mergeCell ref="G352:K352"/>
     <mergeCell ref="G103:K103"/>
     <mergeCell ref="G339:K339"/>
     <mergeCell ref="G118:K118"/>
@@ -9665,7 +9078,6 @@
     <mergeCell ref="G192:K192"/>
     <mergeCell ref="G129:K129"/>
     <mergeCell ref="G63:K63"/>
-    <mergeCell ref="G365:K365"/>
     <mergeCell ref="G50:K50"/>
     <mergeCell ref="G25:K25"/>
     <mergeCell ref="G286:K286"/>
@@ -9681,7 +9093,6 @@
     <mergeCell ref="G78:K78"/>
     <mergeCell ref="G205:K205"/>
     <mergeCell ref="G314:K314"/>
-    <mergeCell ref="G363:K363"/>
     <mergeCell ref="G142:K142"/>
     <mergeCell ref="G80:K80"/>
     <mergeCell ref="B272:K272"/>
@@ -9690,12 +9101,10 @@
     <mergeCell ref="G144:K144"/>
     <mergeCell ref="G119:K119"/>
     <mergeCell ref="G211:K211"/>
-    <mergeCell ref="G358:K358"/>
     <mergeCell ref="G10:K10"/>
     <mergeCell ref="G66:K66"/>
     <mergeCell ref="G308:K308"/>
     <mergeCell ref="G53:K53"/>
-    <mergeCell ref="G360:K360"/>
     <mergeCell ref="B22:K22"/>
     <mergeCell ref="G68:K68"/>
     <mergeCell ref="B93:K93"/>
@@ -9703,15 +9112,13 @@
     <mergeCell ref="G239:K239"/>
     <mergeCell ref="B220:K220"/>
     <mergeCell ref="G310:K310"/>
-    <mergeCell ref="G353:K353"/>
+    <mergeCell ref="B320:K320"/>
     <mergeCell ref="G168:K168"/>
     <mergeCell ref="G213:K213"/>
     <mergeCell ref="G150:K150"/>
     <mergeCell ref="G255:K255"/>
-    <mergeCell ref="G321:K321"/>
     <mergeCell ref="G242:K242"/>
     <mergeCell ref="G81:K81"/>
-    <mergeCell ref="B338:K338"/>
     <mergeCell ref="G244:K244"/>
     <mergeCell ref="G145:K145"/>
     <mergeCell ref="G194:K194"/>
@@ -9721,12 +9128,10 @@
     <mergeCell ref="G18:K18"/>
     <mergeCell ref="G34:K34"/>
     <mergeCell ref="G163:K163"/>
-    <mergeCell ref="G334:K334"/>
     <mergeCell ref="G138:K138"/>
     <mergeCell ref="G113:K113"/>
     <mergeCell ref="G76:K76"/>
     <mergeCell ref="G94:K94"/>
-    <mergeCell ref="G361:K361"/>
     <mergeCell ref="G165:K165"/>
     <mergeCell ref="B172:K172"/>
     <mergeCell ref="G311:K311"/>
@@ -9744,6 +9149,7 @@
     <mergeCell ref="G195:K195"/>
     <mergeCell ref="G95:K95"/>
     <mergeCell ref="G266:K266"/>
+    <mergeCell ref="G322:K322"/>
     <mergeCell ref="G89:K89"/>
     <mergeCell ref="G260:K260"/>
     <mergeCell ref="G309:K309"/>
@@ -9751,6 +9157,7 @@
     <mergeCell ref="G259:K259"/>
     <mergeCell ref="G26:K26"/>
     <mergeCell ref="G153:K153"/>
+    <mergeCell ref="G324:K324"/>
     <mergeCell ref="G90:K90"/>
     <mergeCell ref="G261:K261"/>
     <mergeCell ref="G217:K217"/>
@@ -9758,6 +9165,7 @@
     <mergeCell ref="G115:K115"/>
     <mergeCell ref="G42:K42"/>
     <mergeCell ref="G179:K179"/>
+    <mergeCell ref="B334:K334"/>
     <mergeCell ref="G166:K166"/>
     <mergeCell ref="B173:K173"/>
     <mergeCell ref="G141:K141"/>
@@ -9773,7 +9181,6 @@
     <mergeCell ref="G32:K32"/>
     <mergeCell ref="G330:K330"/>
     <mergeCell ref="G134:K134"/>
-    <mergeCell ref="B349:K349"/>
     <mergeCell ref="G96:K96"/>
     <mergeCell ref="G161:K161"/>
     <mergeCell ref="G332:K332"/>
@@ -9792,11 +9199,9 @@
     <mergeCell ref="G343:K343"/>
     <mergeCell ref="G281:K281"/>
     <mergeCell ref="G188:K188"/>
-    <mergeCell ref="B337:K337"/>
     <mergeCell ref="G280:K280"/>
     <mergeCell ref="G47:K47"/>
     <mergeCell ref="G274:K274"/>
-    <mergeCell ref="G345:K345"/>
     <mergeCell ref="G193:K193"/>
     <mergeCell ref="G295:K295"/>
     <mergeCell ref="G46:K46"/>
@@ -9813,32 +9218,28 @@
     <mergeCell ref="G204:K204"/>
     <mergeCell ref="B58:K58"/>
     <mergeCell ref="G275:K275"/>
-    <mergeCell ref="G335:K335"/>
     <mergeCell ref="B223:K223"/>
-    <mergeCell ref="B350:K350"/>
     <mergeCell ref="G114:K114"/>
     <mergeCell ref="B2:K2"/>
     <mergeCell ref="G206:K206"/>
     <mergeCell ref="B231:K231"/>
     <mergeCell ref="G143:K143"/>
     <mergeCell ref="G270:K270"/>
-    <mergeCell ref="G351:K351"/>
     <mergeCell ref="G59:K59"/>
     <mergeCell ref="G130:K130"/>
     <mergeCell ref="G117:K117"/>
     <mergeCell ref="G67:K67"/>
     <mergeCell ref="G61:K61"/>
     <mergeCell ref="G132:K132"/>
-    <mergeCell ref="G359:K359"/>
     <mergeCell ref="G48:K48"/>
     <mergeCell ref="G224:K224"/>
-    <mergeCell ref="G346:K346"/>
     <mergeCell ref="B305:K305"/>
     <mergeCell ref="G125:K125"/>
     <mergeCell ref="G112:K112"/>
     <mergeCell ref="G283:K283"/>
     <mergeCell ref="G288:K288"/>
     <mergeCell ref="G62:K62"/>
+    <mergeCell ref="G323:K323"/>
     <mergeCell ref="G127:K127"/>
     <mergeCell ref="G298:K298"/>
     <mergeCell ref="B208:K208"/>
@@ -9858,11 +9259,9 @@
     <mergeCell ref="G278:K278"/>
     <mergeCell ref="B232:K232"/>
     <mergeCell ref="G69:K69"/>
-    <mergeCell ref="G354:K354"/>
+    <mergeCell ref="B321:K321"/>
     <mergeCell ref="G133:K133"/>
-    <mergeCell ref="B323:K323"/>
     <mergeCell ref="G225:K225"/>
-    <mergeCell ref="G356:K356"/>
     <mergeCell ref="B229:K229"/>
     <mergeCell ref="G64:K64"/>
     <mergeCell ref="G135:K135"/>
@@ -9872,7 +9271,6 @@
     <mergeCell ref="G226:K226"/>
     <mergeCell ref="B147:K147"/>
     <mergeCell ref="G164:K164"/>
-    <mergeCell ref="G364:K364"/>
     <mergeCell ref="G251:K251"/>
     <mergeCell ref="G17:K17"/>
     <mergeCell ref="G82:K82"/>
@@ -9881,17 +9279,14 @@
     <mergeCell ref="G19:K19"/>
     <mergeCell ref="G317:K317"/>
     <mergeCell ref="G83:K83"/>
-    <mergeCell ref="G319:K319"/>
     <mergeCell ref="G72:K72"/>
     <mergeCell ref="G297:K297"/>
     <mergeCell ref="G136:K136"/>
     <mergeCell ref="G241:K241"/>
     <mergeCell ref="G299:K299"/>
-    <mergeCell ref="G355:K355"/>
     <mergeCell ref="G293:K293"/>
     <mergeCell ref="B197:K197"/>
     <mergeCell ref="G243:K243"/>
-    <mergeCell ref="B324:K324"/>
     <mergeCell ref="G292:K292"/>
     <mergeCell ref="G294:K294"/>
     <mergeCell ref="B184:K184"/>
@@ -9904,7 +9299,6 @@
     <mergeCell ref="G85:K85"/>
     <mergeCell ref="G256:K256"/>
     <mergeCell ref="G84:K84"/>
-    <mergeCell ref="G320:K320"/>
     <mergeCell ref="G149:K149"/>
     <mergeCell ref="G247:K247"/>
     <mergeCell ref="G185:K185"/>
@@ -9916,6 +9310,7 @@
     <mergeCell ref="G13:K13"/>
     <mergeCell ref="G249:K249"/>
     <mergeCell ref="B159:K159"/>
+    <mergeCell ref="G338:K338"/>
     <mergeCell ref="G15:K15"/>
     <mergeCell ref="G313:K313"/>
     <mergeCell ref="G33:K33"/>
@@ -9926,10 +9321,8 @@
     <mergeCell ref="G315:K315"/>
     <mergeCell ref="G35:K35"/>
     <mergeCell ref="G302:K302"/>
-    <mergeCell ref="G333:K333"/>
     <mergeCell ref="G252:K252"/>
     <mergeCell ref="G99:K99"/>
-    <mergeCell ref="G366:K366"/>
     <mergeCell ref="G155:K155"/>
     <mergeCell ref="G170:K170"/>
     <mergeCell ref="G157:K157"/>
@@ -9955,6 +9348,7 @@
     <mergeCell ref="B183:K183"/>
     <mergeCell ref="G316:K316"/>
     <mergeCell ref="G120:K120"/>
+    <mergeCell ref="B335:K335"/>
     <mergeCell ref="G107:K107"/>
     <mergeCell ref="G174:K174"/>
     <mergeCell ref="G189:K189"/>
@@ -9963,13 +9357,13 @@
     <mergeCell ref="G100:K100"/>
     <mergeCell ref="G265:K265"/>
     <mergeCell ref="B290:K290"/>
+    <mergeCell ref="G336:K336"/>
     <mergeCell ref="G44:K44"/>
     <mergeCell ref="G31:K31"/>
     <mergeCell ref="G202:K202"/>
     <mergeCell ref="G102:K102"/>
     <mergeCell ref="G331:K331"/>
     <mergeCell ref="G176:K176"/>
-    <mergeCell ref="G347:K347"/>
     <mergeCell ref="G97:K97"/>
     <mergeCell ref="G268:K268"/>
     <mergeCell ref="G191:K191"/>
@@ -9979,7 +9373,6 @@
     <mergeCell ref="G49:K49"/>
     <mergeCell ref="G342:K342"/>
     <mergeCell ref="G121:K121"/>
-    <mergeCell ref="G357:K357"/>
     <mergeCell ref="G284:K284"/>
     <mergeCell ref="G344:K344"/>
     <mergeCell ref="G123:K123"/>
@@ -9997,7 +9390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H25"/>
+  <dimension ref="B2:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -10536,93 +9929,93 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="33" t="inlineStr">
-        <is>
-          <t>analisis_llm</t>
-        </is>
-      </c>
-      <c r="C18" s="34" t="inlineStr">
-        <is>
-          <t>evaluacion_id</t>
-        </is>
-      </c>
-      <c r="D18" s="34" t="inlineStr">
-        <is>
-          <t>evaluacion_filtro</t>
-        </is>
-      </c>
-      <c r="E18" s="34" t="inlineStr">
+      <c r="B18" s="36" t="inlineStr">
+        <is>
+          <t>oportunidad</t>
+        </is>
+      </c>
+      <c r="C18" s="37" t="inlineStr">
+        <is>
+          <t>origen_licitacion_id</t>
+        </is>
+      </c>
+      <c r="D18" s="37" t="inlineStr">
+        <is>
+          <t>licitacion</t>
+        </is>
+      </c>
+      <c r="E18" s="37" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="F18" s="34" t="inlineStr">
-        <is>
-          <t>1 : 0..N</t>
-        </is>
-      </c>
-      <c r="G18" s="34" t="inlineStr">
-        <is>
-          <t>RESTRICT</t>
-        </is>
-      </c>
-      <c r="H18" s="35" t="inlineStr">
-        <is>
-          <t>FK física</t>
+      <c r="F18" s="37" t="inlineStr">
+        <is>
+          <t>1 : 0..1</t>
+        </is>
+      </c>
+      <c r="G18" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H18" s="38" t="inlineStr">
+        <is>
+          <t>Referencia lógica entre bases (sin FK)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="33" t="inlineStr">
-        <is>
-          <t>analisis_llm</t>
-        </is>
-      </c>
-      <c r="C19" s="34" t="inlineStr">
-        <is>
-          <t>revision_id</t>
-        </is>
-      </c>
-      <c r="D19" s="34" t="inlineStr">
-        <is>
-          <t>revision_manual</t>
-        </is>
-      </c>
-      <c r="E19" s="34" t="inlineStr">
+      <c r="B19" s="36" t="inlineStr">
+        <is>
+          <t>oportunidad</t>
+        </is>
+      </c>
+      <c r="C19" s="37" t="inlineStr">
+        <is>
+          <t>origen_licitacion_id</t>
+        </is>
+      </c>
+      <c r="D19" s="37" t="inlineStr">
+        <is>
+          <t>compra_agil</t>
+        </is>
+      </c>
+      <c r="E19" s="37" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="F19" s="34" t="inlineStr">
-        <is>
-          <t>0..1 : 0..N</t>
-        </is>
-      </c>
-      <c r="G19" s="34" t="inlineStr">
-        <is>
-          <t>RESTRICT</t>
-        </is>
-      </c>
-      <c r="H19" s="35" t="inlineStr">
-        <is>
-          <t>FK física</t>
+      <c r="F19" s="37" t="inlineStr">
+        <is>
+          <t>1 : 0..1</t>
+        </is>
+      </c>
+      <c r="G19" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H19" s="38" t="inlineStr">
+        <is>
+          <t>Referencia lógica entre bases (sin FK)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="36" t="inlineStr">
         <is>
-          <t>oportunidad</t>
+          <t>perfil_filtro_version</t>
         </is>
       </c>
       <c r="C20" s="37" t="inlineStr">
         <is>
-          <t>origen_licitacion_id</t>
+          <t>creado_por</t>
         </is>
       </c>
       <c r="D20" s="37" t="inlineStr">
         <is>
-          <t>licitacion</t>
+          <t>usuario</t>
         </is>
       </c>
       <c r="E20" s="37" t="inlineStr">
@@ -10632,7 +10025,7 @@
       </c>
       <c r="F20" s="37" t="inlineStr">
         <is>
-          <t>1 : 0..1</t>
+          <t>1 : 0..N</t>
         </is>
       </c>
       <c r="G20" s="37" t="inlineStr">
@@ -10647,118 +10040,44 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="36" t="inlineStr">
-        <is>
-          <t>oportunidad</t>
-        </is>
-      </c>
-      <c r="C21" s="37" t="inlineStr">
-        <is>
-          <t>origen_licitacion_id</t>
-        </is>
-      </c>
-      <c r="D21" s="37" t="inlineStr">
-        <is>
-          <t>compra_agil</t>
-        </is>
-      </c>
-      <c r="E21" s="37" t="inlineStr">
+      <c r="B21" s="39" t="inlineStr">
+        <is>
+          <t>revision_manual</t>
+        </is>
+      </c>
+      <c r="C21" s="40" t="inlineStr">
+        <is>
+          <t>revisado_por</t>
+        </is>
+      </c>
+      <c r="D21" s="40" t="inlineStr">
+        <is>
+          <t>usuario</t>
+        </is>
+      </c>
+      <c r="E21" s="40" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="F21" s="37" t="inlineStr">
-        <is>
-          <t>1 : 0..1</t>
-        </is>
-      </c>
-      <c r="G21" s="37" t="inlineStr">
+      <c r="F21" s="40" t="inlineStr">
+        <is>
+          <t>1 : 0..N</t>
+        </is>
+      </c>
+      <c r="G21" s="40" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H21" s="38" t="inlineStr">
+      <c r="H21" s="41" t="inlineStr">
         <is>
           <t>Referencia lógica entre bases (sin FK)</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="36" t="inlineStr">
-        <is>
-          <t>perfil_filtro_version</t>
-        </is>
-      </c>
-      <c r="C22" s="37" t="inlineStr">
-        <is>
-          <t>creado_por</t>
-        </is>
-      </c>
-      <c r="D22" s="37" t="inlineStr">
-        <is>
-          <t>usuario</t>
-        </is>
-      </c>
-      <c r="E22" s="37" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="F22" s="37" t="inlineStr">
-        <is>
-          <t>1 : 0..N</t>
-        </is>
-      </c>
-      <c r="G22" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H22" s="38" t="inlineStr">
-        <is>
-          <t>Referencia lógica entre bases (sin FK)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="39" t="inlineStr">
-        <is>
-          <t>revision_manual</t>
-        </is>
-      </c>
-      <c r="C23" s="40" t="inlineStr">
-        <is>
-          <t>revisado_por</t>
-        </is>
-      </c>
-      <c r="D23" s="40" t="inlineStr">
-        <is>
-          <t>usuario</t>
-        </is>
-      </c>
-      <c r="E23" s="40" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="F23" s="40" t="inlineStr">
-        <is>
-          <t>1 : 0..N</t>
-        </is>
-      </c>
-      <c r="G23" s="40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H23" s="41" t="inlineStr">
-        <is>
-          <t>Referencia lógica entre bases (sin FK)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="45" customHeight="1">
-      <c r="B25" s="2" t="inlineStr">
+    <row r="23" ht="45" customHeight="1">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Las referencias lógicas unen las dos bases de Supabase: LicitacionesFiltradas guarda el id de origen (licitacion.id o compra_agil.id, según oportunidad.modalidad) y el UUID del usuario autenticado. El backend valida estas referencias; PostgreSQL no puede imponer FK entre proyectos distintos.</t>
         </is>
@@ -10767,7 +10086,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B25:H25"/>
+    <mergeCell ref="B23:H23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10779,7 +10098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C8"/>
+  <dimension ref="B2:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -10790,7 +10109,7 @@
     <row r="2">
       <c r="B2" s="29" t="inlineStr">
         <is>
-          <t>Vistas de LicitacionesFiltradas</t>
+          <t>Vista de LicitacionesFiltradas</t>
         </is>
       </c>
     </row>
@@ -10814,43 +10133,7 @@
       </c>
       <c r="C5" s="45" t="inlineStr">
         <is>
-          <t>Cada oportunidad con su última evaluación vigente (perfil activo y versión de datos actual), la revisión manual y el análisis LLM más recientes. Calcula estado_seleccion: pendiente_evaluacion, preseleccionada, revision_manual o descartada; una revisión humana prevalece sobre la propuesta automática.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="B6" s="44" t="inlineStr">
-        <is>
-          <t>vw_licitaciones_filtradas</t>
-        </is>
-      </c>
-      <c r="C6" s="45" t="inlineStr">
-        <is>
-          <t>Licitaciones y Compras Ágiles preseleccionadas por el filtro o recuperadas por un usuario. No implica la aprobación del hotel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="B7" s="44" t="inlineStr">
-        <is>
-          <t>vw_revision_manual</t>
-        </is>
-      </c>
-      <c r="C7" s="45" t="inlineStr">
-        <is>
-          <t>Oportunidades dudosas o sin evaluación vigente (revision_manual o pendiente_evaluacion).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="B8" s="46" t="inlineStr">
-        <is>
-          <t>vw_descartadas</t>
-        </is>
-      </c>
-      <c r="C8" s="47" t="inlineStr">
-        <is>
-          <t>Descartes conservados con su motivo; pueden recuperarse con una revisión nueva.</t>
+          <t>Cada oportunidad con su última evaluación vigente (perfil activo y versión de datos actual) y su revisión manual más reciente. Calcula estado_seleccion: pendiente_evaluacion, preseleccionada, revision_manual o descartada; una revisión humana prevalece sobre la propuesta automática.</t>
         </is>
       </c>
     </row>
